--- a/artfynd/A 38966-2025 artfynd.xlsx
+++ b/artfynd/A 38966-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90799268</v>
+        <v>90799265</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448577.218162724</v>
+        <v>448577</v>
       </c>
       <c r="R2" t="n">
-        <v>7043968.842402861</v>
+        <v>7043969</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2019-07-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90799265</v>
+        <v>90799268</v>
       </c>
       <c r="B3" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -846,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448577.218162724</v>
+        <v>448577</v>
       </c>
       <c r="R3" t="n">
-        <v>7043968.842402861</v>
+        <v>7043969</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,19 +859,9 @@
           <t>2019-07-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -940,12 +910,7 @@
         <v>90799266</v>
       </c>
       <c r="B4" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448577.218162724</v>
+        <v>448577</v>
       </c>
       <c r="R4" t="n">
-        <v>7043968.842402861</v>
+        <v>7043969</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1010,19 +975,9 @@
           <t>2019-07-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1061,6 +1016,122 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>90799313</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tallberget-Acksjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>448603</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7043910</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-07-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-07-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>uppflog</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Naturskog</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
